--- a/現場技術業務_検査受検資料_条文別整理表_9月分.xlsx
+++ b/現場技術業務_検査受検資料_条文別整理表_9月分.xlsx
@@ -2199,7 +2199,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">p / n</t>
+      <t xml:space="preserve">p.○</t>
     </r>
     <r>
       <rPr>
@@ -9319,8 +9319,8 @@
       <c r="F30" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="G30" s="15" t="s">
-        <v>52</v>
+      <c r="G30" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>141</v>
@@ -12865,10 +12865,10 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter>&amp;C条文別整理表　&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;C条文別整理表　p.&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
